--- a/research/traditional_assets/database/data/taiwan/taiwan_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0968</v>
+        <v>0.124</v>
       </c>
       <c r="E2">
-        <v>0.234</v>
+        <v>0.205</v>
       </c>
       <c r="F2">
-        <v>0.214</v>
+        <v>0.145</v>
       </c>
       <c r="G2">
-        <v>0.0198354674098908</v>
+        <v>0.2873969681999012</v>
       </c>
       <c r="H2">
-        <v>0.01888489450795061</v>
+        <v>0.2873969681999012</v>
       </c>
       <c r="I2">
-        <v>0.02791937633800541</v>
+        <v>0.1069450583738527</v>
       </c>
       <c r="J2">
-        <v>0.02167248177080153</v>
+        <v>0.08308661211703504</v>
       </c>
       <c r="K2">
-        <v>2328.69</v>
+        <v>2024.6</v>
       </c>
       <c r="L2">
-        <v>0.3135396049602133</v>
+        <v>0.2632153722145661</v>
       </c>
       <c r="M2">
-        <v>1500.26</v>
+        <v>1053.022</v>
       </c>
       <c r="N2">
-        <v>0.04570187436599639</v>
+        <v>0.04101878722484292</v>
       </c>
       <c r="O2">
-        <v>0.6442506301826348</v>
+        <v>0.5201136026869506</v>
       </c>
       <c r="P2">
-        <v>961.86</v>
+        <v>1053.022</v>
       </c>
       <c r="Q2">
-        <v>0.02930079111465832</v>
+        <v>0.04101878722484292</v>
       </c>
       <c r="R2">
-        <v>0.4130476791672571</v>
+        <v>0.5201136026869506</v>
       </c>
       <c r="S2">
-        <v>538.4</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.3588711290043059</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>4361.77</v>
+        <v>3878.1</v>
       </c>
       <c r="V2">
-        <v>0.1328710120601576</v>
+        <v>0.1510651807242995</v>
       </c>
       <c r="W2">
-        <v>0.193718914095455</v>
+        <v>0.14458753028178</v>
       </c>
       <c r="X2">
-        <v>0.03758443145608806</v>
+        <v>0.07283216814521917</v>
       </c>
       <c r="Y2">
-        <v>0.1561344826393669</v>
+        <v>0.07175536213656078</v>
       </c>
       <c r="Z2">
-        <v>0.1309831460451232</v>
+        <v>0.1187080365362341</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02793071990083514</v>
+        <v>0.05173370126984102</v>
       </c>
       <c r="AC2">
-        <v>-0.02748075858009736</v>
+        <v>-0.05146534878313255</v>
       </c>
       <c r="AD2">
-        <v>56275.27600000001</v>
+        <v>54907.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>56275.27600000001</v>
+        <v>54907.3</v>
       </c>
       <c r="AG2">
-        <v>51913.50600000001</v>
+        <v>51029.2</v>
       </c>
       <c r="AH2">
-        <v>0.6315799704376009</v>
+        <v>0.6814095483935021</v>
       </c>
       <c r="AI2">
-        <v>0.7640971187590239</v>
+        <v>0.7711710269255997</v>
       </c>
       <c r="AJ2">
-        <v>0.6126166480329396</v>
+        <v>0.6653011894254174</v>
       </c>
       <c r="AK2">
-        <v>0.7492466401566825</v>
+        <v>0.7579892397410646</v>
       </c>
       <c r="AL2">
-        <v>0.449</v>
+        <v>0.383</v>
       </c>
       <c r="AM2">
-        <v>-10.025</v>
+        <v>-10.273</v>
       </c>
       <c r="AN2">
-        <v>259.1062019429992</v>
+        <v>62.24611722026982</v>
       </c>
       <c r="AO2">
-        <v>461.8262806236081</v>
+        <v>2147.780678851175</v>
       </c>
       <c r="AP2">
-        <v>239.0234633270409</v>
+        <v>57.84967690738013</v>
       </c>
       <c r="AQ2">
-        <v>-20.68428927680798</v>
+        <v>-80.07398033680521</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SysJust Co., Ltd. (TPEX:3158)</t>
+          <t>Yulon Finance Corporation (TWSE:9941)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,46 +725,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0633</v>
+        <v>0.133</v>
       </c>
       <c r="E3">
-        <v>0.07969999999999999</v>
+        <v>0.225</v>
       </c>
       <c r="G3">
-        <v>0.4736434108527131</v>
+        <v>0.228227412638059</v>
       </c>
       <c r="H3">
-        <v>0.2</v>
+        <v>0.228227412638059</v>
       </c>
       <c r="I3">
-        <v>0.2038759689922481</v>
+        <v>0.2468766974470397</v>
       </c>
       <c r="J3">
-        <v>0.1692350963847156</v>
+        <v>0.1844286490261504</v>
       </c>
       <c r="K3">
-        <v>4.69</v>
+        <v>184.8</v>
       </c>
       <c r="L3">
-        <v>0.1817829457364341</v>
+        <v>0.1673003802281369</v>
       </c>
       <c r="M3">
-        <v>2.36</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N3">
-        <v>0.03376251788268955</v>
+        <v>0.02626977187822907</v>
       </c>
       <c r="O3">
-        <v>0.5031982942430703</v>
+        <v>0.3576839826839826</v>
       </c>
       <c r="P3">
-        <v>2.36</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.03376251788268955</v>
+        <v>0.02626977187822907</v>
       </c>
       <c r="R3">
-        <v>0.5031982942430703</v>
+        <v>0.3576839826839826</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,73 +773,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.57</v>
+        <v>228.5</v>
       </c>
       <c r="V3">
-        <v>0.07968526466380543</v>
+        <v>0.09081154121294016</v>
       </c>
       <c r="W3">
-        <v>0.3423357664233577</v>
+        <v>0.255566311713456</v>
       </c>
       <c r="X3">
-        <v>0.02419037019661267</v>
+        <v>0.07283216814521917</v>
       </c>
       <c r="Y3">
-        <v>0.318145396226745</v>
+        <v>0.1827341435682368</v>
       </c>
       <c r="Z3">
-        <v>3.033509700176367</v>
+        <v>0.158277092378455</v>
       </c>
       <c r="AA3">
-        <v>0.5133763064933173</v>
+        <v>0.02919083031914566</v>
       </c>
       <c r="AB3">
-        <v>0.02417500883992799</v>
+        <v>0.05173370126984102</v>
       </c>
       <c r="AC3">
-        <v>0.4892012976533894</v>
+        <v>-0.02254287095069536</v>
       </c>
       <c r="AD3">
-        <v>0.776</v>
+        <v>6614.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.776</v>
+        <v>6614.2</v>
       </c>
       <c r="AG3">
-        <v>-4.794</v>
+        <v>6385.7</v>
       </c>
       <c r="AH3">
-        <v>0.01097968192880186</v>
+        <v>0.7244151406291072</v>
       </c>
       <c r="AI3">
-        <v>0.03943891034763164</v>
+        <v>0.8571502624246744</v>
       </c>
       <c r="AJ3">
-        <v>-0.07363376647313612</v>
+        <v>0.7173412417573777</v>
       </c>
       <c r="AK3">
-        <v>-0.3398553806890686</v>
+        <v>0.8527911324786325</v>
       </c>
       <c r="AL3">
-        <v>0.033</v>
+        <v>0.383</v>
       </c>
       <c r="AM3">
-        <v>-0.02</v>
+        <v>0.383</v>
       </c>
       <c r="AN3">
-        <v>0.1274220032840722</v>
+        <v>23.11041229909155</v>
       </c>
       <c r="AO3">
-        <v>159.3939393939394</v>
+        <v>712.0104438642297</v>
       </c>
       <c r="AP3">
-        <v>-0.7871921182266011</v>
+        <v>22.31201956673655</v>
       </c>
       <c r="AQ3">
-        <v>-263.0000000000001</v>
+        <v>712.0104438642297</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yulon Finance Corporation (TWSE:9941)</t>
+          <t>Yuanta Financial Holding Co., Ltd. (TWSE:2885)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,46 +859,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.123</v>
+        <v>0.0273</v>
       </c>
       <c r="E4">
-        <v>0.242</v>
+        <v>0.108</v>
       </c>
       <c r="G4">
-        <v>0.121242035358521</v>
+        <v>0.5217101758124667</v>
       </c>
       <c r="H4">
-        <v>0.121242035358521</v>
+        <v>0.5217101758124667</v>
       </c>
       <c r="I4">
-        <v>0.1813694696221843</v>
+        <v>0.1464837506659563</v>
       </c>
       <c r="J4">
-        <v>0.1400623559666055</v>
+        <v>0.1216259893020862</v>
       </c>
       <c r="K4">
-        <v>163.5</v>
+        <v>822.8</v>
       </c>
       <c r="L4">
-        <v>0.1467288880911783</v>
+        <v>0.2191795418220565</v>
       </c>
       <c r="M4">
-        <v>56.1</v>
+        <v>572.7</v>
       </c>
       <c r="N4">
-        <v>0.01844181459566075</v>
+        <v>0.06485403030371663</v>
       </c>
       <c r="O4">
-        <v>0.3431192660550459</v>
+        <v>0.6960379192999515</v>
       </c>
       <c r="P4">
-        <v>56.1</v>
+        <v>572.7</v>
       </c>
       <c r="Q4">
-        <v>0.01844181459566075</v>
+        <v>0.06485403030371663</v>
       </c>
       <c r="R4">
-        <v>0.3431192660550459</v>
+        <v>0.6960379192999515</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -907,73 +907,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>241.7</v>
+        <v>1896.7</v>
       </c>
       <c r="V4">
-        <v>0.07945430637738329</v>
+        <v>0.2147872171766358</v>
       </c>
       <c r="W4">
-        <v>0.2733199598796389</v>
+        <v>0.08743889479277364</v>
       </c>
       <c r="X4">
-        <v>0.03942165742415134</v>
+        <v>0.06379578891022246</v>
       </c>
       <c r="Y4">
-        <v>0.2338983024554876</v>
+        <v>0.02364310588255118</v>
       </c>
       <c r="Z4">
-        <v>0.1872206727376592</v>
+        <v>0.1747111030441804</v>
       </c>
       <c r="AA4">
-        <v>0.02622256850928937</v>
+        <v>0.02124941074980716</v>
       </c>
       <c r="AB4">
-        <v>0.0281144976148006</v>
+        <v>0.05143732249030138</v>
       </c>
       <c r="AC4">
-        <v>-0.001891929105511232</v>
+        <v>-0.03018791174049422</v>
       </c>
       <c r="AD4">
-        <v>6461.6</v>
+        <v>14118.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>6461.6</v>
+        <v>14118.1</v>
       </c>
       <c r="AG4">
-        <v>6219.900000000001</v>
+        <v>12221.4</v>
       </c>
       <c r="AH4">
-        <v>0.6799107706553307</v>
+        <v>0.6152026040690758</v>
       </c>
       <c r="AI4">
-        <v>0.8825393356643356</v>
+        <v>0.6258855344239039</v>
       </c>
       <c r="AJ4">
-        <v>0.6715576717520163</v>
+        <v>0.5805339160174805</v>
       </c>
       <c r="AK4">
-        <v>0.8785293577592904</v>
+        <v>0.5915402970915233</v>
       </c>
       <c r="AL4">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.416</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>30.60918995736618</v>
-      </c>
-      <c r="AO4">
-        <v>485.8173076923077</v>
+        <v>23.69206242658164</v>
       </c>
       <c r="AP4">
-        <v>29.46423495973472</v>
-      </c>
-      <c r="AQ4">
-        <v>485.8173076923077</v>
+        <v>20.50914582983722</v>
       </c>
     </row>
     <row r="5">
@@ -993,13 +987,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0968</v>
+        <v>0.124</v>
       </c>
       <c r="E5">
-        <v>0.234</v>
+        <v>0.248</v>
       </c>
       <c r="F5">
-        <v>0.214</v>
+        <v>0.145</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1014,85 +1008,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>736.7</v>
+        <v>840.2</v>
       </c>
       <c r="L5">
-        <v>0.3890473172792565</v>
+        <v>0.4239366264695494</v>
       </c>
       <c r="M5">
-        <v>786.5</v>
+        <v>284.922</v>
       </c>
       <c r="N5">
-        <v>0.05173082867986082</v>
+        <v>0.02548269385564798</v>
       </c>
       <c r="O5">
-        <v>1.067598751187729</v>
+        <v>0.3391121161628184</v>
       </c>
       <c r="P5">
-        <v>248.1</v>
+        <v>284.922</v>
       </c>
       <c r="Q5">
-        <v>0.01631839617987726</v>
+        <v>0.02548269385564798</v>
       </c>
       <c r="R5">
-        <v>0.3367720917605538</v>
+        <v>0.3391121161628184</v>
       </c>
       <c r="S5">
-        <v>538.4</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.6845518118245391</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1375.1</v>
+        <v>1581.3</v>
       </c>
       <c r="V5">
-        <v>0.09044508902438221</v>
+        <v>0.1414274215186477</v>
       </c>
       <c r="W5">
-        <v>0.2399517946713569</v>
+        <v>0.2295816596988824</v>
       </c>
       <c r="X5">
-        <v>0.03214486193487914</v>
+        <v>0.06442464508268991</v>
       </c>
       <c r="Y5">
-        <v>0.2078069327364778</v>
+        <v>0.1651570146161925</v>
       </c>
       <c r="Z5">
-        <v>0.1224298207388461</v>
+        <v>0.1027845543634297</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.02721457497332506</v>
+        <v>0.05146534878313255</v>
       </c>
       <c r="AC5">
-        <v>-0.02721457497332506</v>
+        <v>-0.05146534878313255</v>
       </c>
       <c r="AD5">
-        <v>16946.4</v>
+        <v>18677.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>16946.4</v>
+        <v>18677.2</v>
       </c>
       <c r="AG5">
-        <v>15571.3</v>
+        <v>17095.9</v>
       </c>
       <c r="AH5">
-        <v>0.5271025595565799</v>
+        <v>0.6255300051577122</v>
       </c>
       <c r="AI5">
-        <v>0.8121654198037929</v>
+        <v>0.8040051312515605</v>
       </c>
       <c r="AJ5">
-        <v>0.5059723801787165</v>
+        <v>0.604588904724351</v>
       </c>
       <c r="AK5">
-        <v>0.7989133223194771</v>
+        <v>0.7896890835100167</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1112,7 +1106,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yuanta Financial Holding Co., Ltd (TWSE:2885)</t>
+          <t>Hotai Finance Co., Ltd. (TWSE:6592)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,10 +1115,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0809</v>
+        <v>0.151</v>
       </c>
       <c r="E6">
-        <v>0.249</v>
+        <v>0.205</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1139,28 +1133,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1180</v>
+        <v>113.4</v>
       </c>
       <c r="L6">
-        <v>0.3395194935980435</v>
+        <v>0.1789772727272727</v>
       </c>
       <c r="M6">
-        <v>523.2</v>
+        <v>68</v>
       </c>
       <c r="N6">
-        <v>0.04725817669427609</v>
+        <v>0.03624926701849779</v>
       </c>
       <c r="O6">
-        <v>0.4433898305084746</v>
+        <v>0.5996472663139329</v>
       </c>
       <c r="P6">
-        <v>523.2</v>
+        <v>68</v>
       </c>
       <c r="Q6">
-        <v>0.04725817669427609</v>
+        <v>0.03624926701849779</v>
       </c>
       <c r="R6">
-        <v>0.4433898305084746</v>
+        <v>0.5996472663139329</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1169,61 +1163,64 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2633</v>
+        <v>68.7</v>
       </c>
       <c r="V6">
-        <v>0.2378264129128994</v>
+        <v>0.03662242123780585</v>
       </c>
       <c r="W6">
-        <v>0.1385431832057483</v>
+        <v>0.14458753028178</v>
       </c>
       <c r="X6">
-        <v>0.03574720548802478</v>
+        <v>0.07886792309964563</v>
       </c>
       <c r="Y6">
-        <v>0.1027959777177236</v>
+        <v>0.06571960718213432</v>
       </c>
       <c r="Z6">
-        <v>0.1654456392899476</v>
+        <v>0.09888257693988389</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.02774694218686966</v>
+        <v>0.05185288479363083</v>
       </c>
       <c r="AC6">
-        <v>-0.02774694218686966</v>
+        <v>-0.05185288479363083</v>
       </c>
       <c r="AD6">
-        <v>17872.9</v>
+        <v>6221.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>17872.9</v>
+        <v>6221.5</v>
       </c>
       <c r="AG6">
-        <v>15239.9</v>
+        <v>6152.8</v>
       </c>
       <c r="AH6">
-        <v>0.6174993090105031</v>
+        <v>0.7683330451749945</v>
       </c>
       <c r="AI6">
-        <v>0.637951035297561</v>
+        <v>0.8611907035975803</v>
       </c>
       <c r="AJ6">
-        <v>0.5792216183345369</v>
+        <v>0.7663507168034676</v>
       </c>
       <c r="AK6">
-        <v>0.6003955387639808</v>
+        <v>0.8598580133042651</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>-0.456</v>
+      </c>
+      <c r="AQ6">
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -1234,7 +1231,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hotai Finance Co., Ltd. (TWSE:6592)</t>
+          <t>IBF Financial Holdings Co., Ltd. (TWSE:2889)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1242,6 +1239,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.0472</v>
+      </c>
+      <c r="E7">
+        <v>0.0032</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1255,28 +1258,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>105.6</v>
+        <v>63.4</v>
       </c>
       <c r="L7">
-        <v>0.1872672459655967</v>
+        <v>0.2912264584290308</v>
       </c>
       <c r="M7">
-        <v>64.7</v>
+        <v>61.3</v>
       </c>
       <c r="N7">
-        <v>0.03779426368362638</v>
+        <v>0.04834384858044164</v>
       </c>
       <c r="O7">
-        <v>0.612689393939394</v>
+        <v>0.9668769716088328</v>
       </c>
       <c r="P7">
-        <v>64.7</v>
+        <v>61.3</v>
       </c>
       <c r="Q7">
-        <v>0.03779426368362638</v>
+        <v>0.04834384858044164</v>
       </c>
       <c r="R7">
-        <v>0.612689393939394</v>
+        <v>0.9668769716088328</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1285,185 +1288,60 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>25.4</v>
+        <v>102.9</v>
       </c>
       <c r="V7">
-        <v>0.01483731526374204</v>
+        <v>0.08115141955835962</v>
       </c>
       <c r="W7">
-        <v>0.1474860335195531</v>
+        <v>0.04586226851851852</v>
       </c>
       <c r="X7">
-        <v>0.04789526288566756</v>
+        <v>0.1139574417415955</v>
       </c>
       <c r="Y7">
-        <v>0.09959077063388549</v>
+        <v>-0.06809517322307702</v>
       </c>
       <c r="Z7">
-        <v>0.1152109510675248</v>
+        <v>0.02045962255426687</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.0286298822407049</v>
+        <v>0.05215523354458076</v>
       </c>
       <c r="AC7">
-        <v>-0.0286298822407049</v>
+        <v>-0.05215523354458076</v>
       </c>
       <c r="AD7">
-        <v>5648.7</v>
+        <v>9276.299999999999</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>5648.7</v>
+        <v>9276.299999999999</v>
       </c>
       <c r="AG7">
-        <v>5623.3</v>
+        <v>9173.4</v>
       </c>
       <c r="AH7">
-        <v>0.7674238513164687</v>
+        <v>0.8797454548903199</v>
       </c>
       <c r="AI7">
-        <v>0.8665909823113388</v>
+        <v>0.8858277867435709</v>
       </c>
       <c r="AJ7">
-        <v>0.7666184971098265</v>
+        <v>0.8785603463137127</v>
       </c>
       <c r="AK7">
-        <v>0.8660690908530856</v>
+        <v>0.8846947632365705</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.221</v>
-      </c>
-      <c r="AQ7">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>IBF Financial Holdings Co., Ltd. (TWSE:2889)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.12</v>
-      </c>
-      <c r="E8">
-        <v>0.118</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>138.2</v>
-      </c>
-      <c r="L8">
-        <v>0.3903954802259887</v>
-      </c>
-      <c r="M8">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="N8">
-        <v>0.03899334683251374</v>
-      </c>
-      <c r="O8">
-        <v>0.487698986975398</v>
-      </c>
-      <c r="P8">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="Q8">
-        <v>0.03899334683251374</v>
-      </c>
-      <c r="R8">
-        <v>0.487698986975398</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>81</v>
-      </c>
-      <c r="V8">
-        <v>0.04686144055539485</v>
-      </c>
-      <c r="W8">
-        <v>0.1082393483709273</v>
-      </c>
-      <c r="X8">
-        <v>0.063080918643936</v>
-      </c>
-      <c r="Y8">
-        <v>0.04515842972699131</v>
-      </c>
-      <c r="Z8">
-        <v>0.03776326274590125</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.02908029854819576</v>
-      </c>
-      <c r="AC8">
-        <v>-0.02908029854819576</v>
-      </c>
-      <c r="AD8">
-        <v>9344.9</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>9344.9</v>
-      </c>
-      <c r="AG8">
-        <v>9263.9</v>
-      </c>
-      <c r="AH8">
-        <v>0.8439052142973251</v>
-      </c>
-      <c r="AI8">
-        <v>0.8567015034836817</v>
-      </c>
-      <c r="AJ8">
-        <v>0.8427549943597394</v>
-      </c>
-      <c r="AK8">
-        <v>0.8556294449062528</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/taiwan/taiwan_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.124</v>
+        <v>0.02855</v>
       </c>
       <c r="E2">
-        <v>0.205</v>
+        <v>0.119</v>
       </c>
       <c r="F2">
-        <v>0.145</v>
+        <v>0.149</v>
       </c>
       <c r="G2">
-        <v>0.2873969681999012</v>
+        <v>0.0857622815054936</v>
       </c>
       <c r="H2">
-        <v>0.2873969681999012</v>
+        <v>0.08520677885136253</v>
       </c>
       <c r="I2">
-        <v>0.1069450583738527</v>
+        <v>0.1219561293135991</v>
       </c>
       <c r="J2">
-        <v>0.08308661211703504</v>
+        <v>0.1024730140768701</v>
       </c>
       <c r="K2">
-        <v>2024.6</v>
+        <v>1971.48</v>
       </c>
       <c r="L2">
-        <v>0.2632153722145661</v>
+        <v>0.2229565090729461</v>
       </c>
       <c r="M2">
-        <v>1053.022</v>
+        <v>791.7664</v>
       </c>
       <c r="N2">
-        <v>0.04101878722484292</v>
+        <v>0.02596346990037842</v>
       </c>
       <c r="O2">
-        <v>0.5201136026869506</v>
+        <v>0.4016101608943535</v>
       </c>
       <c r="P2">
-        <v>1053.022</v>
+        <v>791.7664</v>
       </c>
       <c r="Q2">
-        <v>0.04101878722484292</v>
+        <v>0.02596346990037842</v>
       </c>
       <c r="R2">
-        <v>0.5201136026869506</v>
+        <v>0.4016101608943535</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3878.1</v>
+        <v>3977.78</v>
       </c>
       <c r="V2">
-        <v>0.1510651807242995</v>
+        <v>0.130438689113768</v>
       </c>
       <c r="W2">
-        <v>0.14458753028178</v>
+        <v>0.06850934425814936</v>
       </c>
       <c r="X2">
-        <v>0.07283216814521917</v>
+        <v>0.05706392424678296</v>
       </c>
       <c r="Y2">
-        <v>0.07175536213656078</v>
+        <v>0.01144542001136641</v>
       </c>
       <c r="Z2">
-        <v>0.1187080365362341</v>
+        <v>0.1351031790166068</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.01405763500971453</v>
       </c>
       <c r="AB2">
-        <v>0.05173370126984102</v>
+        <v>0.05186322534054851</v>
       </c>
       <c r="AC2">
-        <v>-0.05146534878313255</v>
+        <v>-0.03773462372007374</v>
       </c>
       <c r="AD2">
-        <v>54907.3</v>
+        <v>60337.683</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>54907.3</v>
+        <v>60337.683</v>
       </c>
       <c r="AG2">
-        <v>51029.2</v>
+        <v>56359.90300000001</v>
       </c>
       <c r="AH2">
-        <v>0.6814095483935021</v>
+        <v>0.6642699004282393</v>
       </c>
       <c r="AI2">
-        <v>0.7711710269255997</v>
+        <v>0.766340881386566</v>
       </c>
       <c r="AJ2">
-        <v>0.6653011894254174</v>
+        <v>0.6488942074152916</v>
       </c>
       <c r="AK2">
-        <v>0.7579892397410646</v>
+        <v>0.7539080051135812</v>
       </c>
       <c r="AL2">
-        <v>0.383</v>
+        <v>2.704</v>
       </c>
       <c r="AM2">
-        <v>-10.273</v>
+        <v>-18.724</v>
       </c>
       <c r="AN2">
-        <v>62.24611722026982</v>
+        <v>52.37136927659811</v>
       </c>
       <c r="AO2">
-        <v>2147.780678851175</v>
+        <v>398.8128698224852</v>
       </c>
       <c r="AP2">
-        <v>57.84967690738013</v>
+        <v>48.91877091810519</v>
       </c>
       <c r="AQ2">
-        <v>-80.07398033680521</v>
+        <v>-57.59399700918608</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yulon Finance Corporation (TWSE:9941)</t>
+          <t>Green World Fintech Service Co., Ltd. (TPEX:6763)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,47 +724,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.133</v>
-      </c>
-      <c r="E3">
-        <v>0.225</v>
-      </c>
       <c r="G3">
-        <v>0.228227412638059</v>
+        <v>0.3399585921325052</v>
       </c>
       <c r="H3">
-        <v>0.228227412638059</v>
+        <v>0.2898550724637681</v>
       </c>
       <c r="I3">
-        <v>0.2468766974470397</v>
+        <v>0.277432712215321</v>
       </c>
       <c r="J3">
-        <v>0.1844286490261504</v>
+        <v>0.2241221126131613</v>
       </c>
       <c r="K3">
-        <v>184.8</v>
+        <v>12.3</v>
       </c>
       <c r="L3">
-        <v>0.1673003802281369</v>
+        <v>0.2546583850931677</v>
       </c>
       <c r="M3">
-        <v>66.09999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="N3">
-        <v>0.02626977187822907</v>
+        <v>0.03108206245461148</v>
       </c>
       <c r="O3">
-        <v>0.3576839826839826</v>
+        <v>0.6959349593495935</v>
       </c>
       <c r="P3">
-        <v>66.09999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="Q3">
-        <v>0.02626977187822907</v>
+        <v>0.03108206245461148</v>
       </c>
       <c r="R3">
-        <v>0.3576839826839826</v>
+        <v>0.6959349593495935</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,73 +767,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>228.5</v>
+        <v>28.1</v>
       </c>
       <c r="V3">
-        <v>0.09081154121294016</v>
+        <v>0.1020334059549746</v>
       </c>
       <c r="W3">
-        <v>0.255566311713456</v>
+        <v>0.1574903969270167</v>
       </c>
       <c r="X3">
-        <v>0.07283216814521917</v>
+        <v>0.05204096976291783</v>
       </c>
       <c r="Y3">
-        <v>0.1827341435682368</v>
+        <v>0.1054494271640988</v>
       </c>
       <c r="Z3">
-        <v>0.158277092378455</v>
+        <v>0.9156398104265405</v>
       </c>
       <c r="AA3">
-        <v>0.02919083031914566</v>
+        <v>0.2052151287055107</v>
       </c>
       <c r="AB3">
-        <v>0.05173370126984102</v>
+        <v>0.05196922370842263</v>
       </c>
       <c r="AC3">
-        <v>-0.02254287095069536</v>
+        <v>0.1532459049970881</v>
       </c>
       <c r="AD3">
-        <v>6614.2</v>
+        <v>3.26</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6614.2</v>
+        <v>3.26</v>
       </c>
       <c r="AG3">
-        <v>6385.7</v>
+        <v>-24.84</v>
       </c>
       <c r="AH3">
-        <v>0.7244151406291072</v>
+        <v>0.0116988444699634</v>
       </c>
       <c r="AI3">
-        <v>0.8571502624246744</v>
+        <v>0.0351823872221023</v>
       </c>
       <c r="AJ3">
-        <v>0.7173412417573777</v>
+        <v>-0.09913793103448278</v>
       </c>
       <c r="AK3">
-        <v>0.8527911324786325</v>
+        <v>-0.3847583643122677</v>
       </c>
       <c r="AL3">
-        <v>0.383</v>
+        <v>0.011</v>
       </c>
       <c r="AM3">
-        <v>0.383</v>
+        <v>-1.319</v>
       </c>
       <c r="AN3">
-        <v>23.11041229909155</v>
+        <v>0.2397058823529412</v>
       </c>
       <c r="AO3">
-        <v>712.0104438642297</v>
+        <v>1218.181818181818</v>
       </c>
       <c r="AP3">
-        <v>22.31201956673655</v>
+        <v>-1.826470588235295</v>
       </c>
       <c r="AQ3">
-        <v>712.0104438642297</v>
+        <v>-10.15921152388173</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yuanta Financial Holding Co., Ltd. (TWSE:2885)</t>
+          <t>Transart Graphics Co., Ltd. (TWSE:8481)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,46 +853,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0273</v>
+        <v>-0.0118</v>
       </c>
       <c r="E4">
-        <v>0.108</v>
+        <v>-0.0892</v>
       </c>
       <c r="G4">
-        <v>0.5217101758124667</v>
+        <v>0.4522658610271904</v>
       </c>
       <c r="H4">
-        <v>0.5217101758124667</v>
+        <v>0.4169184290030212</v>
       </c>
       <c r="I4">
-        <v>0.1464837506659563</v>
+        <v>0.1685800604229607</v>
       </c>
       <c r="J4">
-        <v>0.1216259893020862</v>
+        <v>0.1187534415787359</v>
       </c>
       <c r="K4">
-        <v>822.8</v>
+        <v>4.29</v>
       </c>
       <c r="L4">
-        <v>0.2191795418220565</v>
+        <v>0.129607250755287</v>
       </c>
       <c r="M4">
-        <v>572.7</v>
+        <v>7.86</v>
       </c>
       <c r="N4">
-        <v>0.06485403030371663</v>
+        <v>0.07074707470747076</v>
       </c>
       <c r="O4">
-        <v>0.6960379192999515</v>
+        <v>1.832167832167832</v>
       </c>
       <c r="P4">
-        <v>572.7</v>
+        <v>7.86</v>
       </c>
       <c r="Q4">
-        <v>0.06485403030371663</v>
+        <v>0.07074707470747076</v>
       </c>
       <c r="R4">
-        <v>0.6960379192999515</v>
+        <v>1.832167832167832</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -907,67 +901,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1896.7</v>
+        <v>23.3</v>
       </c>
       <c r="V4">
-        <v>0.2147872171766358</v>
+        <v>0.2097209720972097</v>
       </c>
       <c r="W4">
-        <v>0.08743889479277364</v>
+        <v>0.07973977695167286</v>
       </c>
       <c r="X4">
-        <v>0.06379578891022246</v>
+        <v>0.0519482077735824</v>
       </c>
       <c r="Y4">
-        <v>0.02364310588255118</v>
+        <v>0.02779156917809047</v>
       </c>
       <c r="Z4">
-        <v>0.1747111030441804</v>
+        <v>1.115943494824854</v>
       </c>
       <c r="AA4">
-        <v>0.02124941074980716</v>
+        <v>0.1325221306178536</v>
       </c>
       <c r="AB4">
-        <v>0.05143732249030138</v>
+        <v>0.05191626362919237</v>
       </c>
       <c r="AC4">
-        <v>-0.03018791174049422</v>
+        <v>0.08060586698866128</v>
       </c>
       <c r="AD4">
-        <v>14118.1</v>
+        <v>0.333</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>14118.1</v>
+        <v>0.333</v>
       </c>
       <c r="AG4">
-        <v>12221.4</v>
+        <v>-22.967</v>
       </c>
       <c r="AH4">
-        <v>0.6152026040690758</v>
+        <v>0.002988342770992435</v>
       </c>
       <c r="AI4">
-        <v>0.6258855344239039</v>
+        <v>0.006629108355065396</v>
       </c>
       <c r="AJ4">
-        <v>0.5805339160174805</v>
+        <v>-0.260594782884958</v>
       </c>
       <c r="AK4">
-        <v>0.5915402970915233</v>
+        <v>-0.8527457022982959</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-0.403</v>
       </c>
       <c r="AN4">
-        <v>23.69206242658164</v>
+        <v>0.04847161572052402</v>
+      </c>
+      <c r="AO4">
+        <v>558</v>
       </c>
       <c r="AP4">
-        <v>20.50914582983722</v>
+        <v>-3.343085880640466</v>
+      </c>
+      <c r="AQ4">
+        <v>-13.84615384615385</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chailease Holding Company Limited (TWSE:5871)</t>
+          <t>Bai Sha Technology Co., Ltd. (TPEX:8401)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,49 +987,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.124</v>
+        <v>0.0117</v>
       </c>
       <c r="E5">
-        <v>0.248</v>
-      </c>
-      <c r="F5">
-        <v>0.145</v>
+        <v>0.109</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.1672823779193206</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.164968152866242</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.08322717622080679</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.06649481964377775</v>
       </c>
       <c r="K5">
-        <v>840.2</v>
+        <v>3.06</v>
       </c>
       <c r="L5">
-        <v>0.4239366264695494</v>
+        <v>0.06496815286624204</v>
       </c>
       <c r="M5">
-        <v>284.922</v>
+        <v>3.73</v>
       </c>
       <c r="N5">
-        <v>0.02548269385564798</v>
+        <v>0.09031476997578693</v>
       </c>
       <c r="O5">
-        <v>0.3391121161628184</v>
+        <v>1.218954248366013</v>
       </c>
       <c r="P5">
-        <v>284.922</v>
+        <v>3.73</v>
       </c>
       <c r="Q5">
-        <v>0.02548269385564798</v>
+        <v>0.09031476997578693</v>
       </c>
       <c r="R5">
-        <v>0.3391121161628184</v>
+        <v>1.218954248366013</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1038,64 +1035,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1581.3</v>
+        <v>9.65</v>
       </c>
       <c r="V5">
-        <v>0.1414274215186477</v>
+        <v>0.2336561743341405</v>
       </c>
       <c r="W5">
-        <v>0.2295816596988824</v>
+        <v>0.1006578947368421</v>
       </c>
       <c r="X5">
-        <v>0.06442464508268991</v>
+        <v>0.05306772740442633</v>
       </c>
       <c r="Y5">
-        <v>0.1651570146161925</v>
+        <v>0.04759016733241578</v>
       </c>
       <c r="Z5">
-        <v>0.1027845543634297</v>
+        <v>1.949503311258278</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.1296318710770668</v>
       </c>
       <c r="AB5">
-        <v>0.05146534878313255</v>
+        <v>0.05190047354279585</v>
       </c>
       <c r="AC5">
-        <v>-0.05146534878313255</v>
+        <v>0.07773139753427091</v>
       </c>
       <c r="AD5">
-        <v>18677.2</v>
+        <v>4.53</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>18677.2</v>
+        <v>4.53</v>
       </c>
       <c r="AG5">
-        <v>17095.9</v>
+        <v>-5.12</v>
       </c>
       <c r="AH5">
-        <v>0.6255300051577122</v>
+        <v>0.09884355225834607</v>
       </c>
       <c r="AI5">
-        <v>0.8040051312515605</v>
+        <v>0.1331178372024684</v>
       </c>
       <c r="AJ5">
-        <v>0.604588904724351</v>
+        <v>-0.1415146489773355</v>
       </c>
       <c r="AK5">
-        <v>0.7896890835100167</v>
+        <v>-0.2100082034454471</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.101</v>
       </c>
       <c r="AM5">
-        <v>-10.2</v>
+        <v>0.063</v>
+      </c>
+      <c r="AN5">
+        <v>0.7012383900928792</v>
+      </c>
+      <c r="AO5">
+        <v>38.81188118811881</v>
+      </c>
+      <c r="AP5">
+        <v>-0.7925696594427245</v>
       </c>
       <c r="AQ5">
-        <v>-0</v>
+        <v>62.22222222222222</v>
       </c>
     </row>
     <row r="6">
@@ -1106,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hotai Finance Co., Ltd. (TWSE:6592)</t>
+          <t>Top High Image Corp. (TPEX:3284)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1115,46 +1121,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.151</v>
+        <v>-0.0353</v>
       </c>
       <c r="E6">
-        <v>0.205</v>
+        <v>0.137</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.08536796536796536</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.08398268398268398</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.09437229437229437</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.07942625157936162</v>
       </c>
       <c r="K6">
-        <v>113.4</v>
+        <v>1.76</v>
       </c>
       <c r="L6">
-        <v>0.1789772727272727</v>
+        <v>0.07619047619047618</v>
       </c>
       <c r="M6">
-        <v>68</v>
+        <v>0.273</v>
       </c>
       <c r="N6">
-        <v>0.03624926701849779</v>
+        <v>0.005735294117647059</v>
       </c>
       <c r="O6">
-        <v>0.5996472663139329</v>
+        <v>0.1551136363636364</v>
       </c>
       <c r="P6">
-        <v>68</v>
+        <v>0.273</v>
       </c>
       <c r="Q6">
-        <v>0.03624926701849779</v>
+        <v>0.005735294117647059</v>
       </c>
       <c r="R6">
-        <v>0.5996472663139329</v>
+        <v>0.1551136363636364</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1163,64 +1169,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>68.7</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="V6">
-        <v>0.03662242123780585</v>
+        <v>0.1920168067226891</v>
       </c>
       <c r="W6">
-        <v>0.14458753028178</v>
+        <v>0.056957928802589</v>
       </c>
       <c r="X6">
-        <v>0.07886792309964563</v>
+        <v>0.05584076017885557</v>
       </c>
       <c r="Y6">
-        <v>0.06571960718213432</v>
+        <v>0.001117168623733428</v>
       </c>
       <c r="Z6">
-        <v>0.09888257693988389</v>
+        <v>0.5894360806328146</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.04681669843029482</v>
       </c>
       <c r="AB6">
-        <v>0.05185288479363083</v>
+        <v>0.05187192152775932</v>
       </c>
       <c r="AC6">
-        <v>-0.05185288479363083</v>
+        <v>-0.005055223097464506</v>
       </c>
       <c r="AD6">
-        <v>6221.5</v>
+        <v>17.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>6221.5</v>
+        <v>17.8</v>
       </c>
       <c r="AG6">
-        <v>6152.8</v>
+        <v>8.66</v>
       </c>
       <c r="AH6">
-        <v>0.7683330451749945</v>
+        <v>0.27217125382263</v>
       </c>
       <c r="AI6">
-        <v>0.8611907035975803</v>
+        <v>0.3483365949119374</v>
       </c>
       <c r="AJ6">
-        <v>0.7663507168034676</v>
+        <v>0.1539281905439033</v>
       </c>
       <c r="AK6">
-        <v>0.8598580133042651</v>
+        <v>0.2063870352716874</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="AM6">
-        <v>-0.456</v>
+        <v>0.363</v>
+      </c>
+      <c r="AN6">
+        <v>7.063492063492064</v>
+      </c>
+      <c r="AO6">
+        <v>5.240384615384616</v>
+      </c>
+      <c r="AP6">
+        <v>3.436507936507937</v>
       </c>
       <c r="AQ6">
-        <v>-0</v>
+        <v>6.005509641873279</v>
       </c>
     </row>
     <row r="7">
@@ -1231,118 +1246,1279 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Taiwan Name Plate Co., Ltd. (TPEX:6593)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>-0.0405</v>
+      </c>
+      <c r="E7">
+        <v>-0.106</v>
+      </c>
+      <c r="G7">
+        <v>0.09042553191489361</v>
+      </c>
+      <c r="H7">
+        <v>0.05372340425531915</v>
+      </c>
+      <c r="I7">
+        <v>0.06489361702127659</v>
+      </c>
+      <c r="J7">
+        <v>0.05100517001391926</v>
+      </c>
+      <c r="K7">
+        <v>0.842</v>
+      </c>
+      <c r="L7">
+        <v>0.04478723404255319</v>
+      </c>
+      <c r="M7">
+        <v>0.3664</v>
+      </c>
+      <c r="N7">
+        <v>0.003402042711234912</v>
+      </c>
+      <c r="O7">
+        <v>0.4351543942992874</v>
+      </c>
+      <c r="P7">
+        <v>0.3664</v>
+      </c>
+      <c r="Q7">
+        <v>0.003402042711234912</v>
+      </c>
+      <c r="R7">
+        <v>0.4351543942992874</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>5.84</v>
+      </c>
+      <c r="V7">
+        <v>0.05422469823584029</v>
+      </c>
+      <c r="W7">
+        <v>0.05727891156462585</v>
+      </c>
+      <c r="X7">
+        <v>0.05253252486198652</v>
+      </c>
+      <c r="Y7">
+        <v>0.004746386702639327</v>
+      </c>
+      <c r="Z7">
+        <v>0.9130645944633318</v>
+      </c>
+      <c r="AA7">
+        <v>0.04657101487429249</v>
+      </c>
+      <c r="AB7">
+        <v>0.05216534726246534</v>
+      </c>
+      <c r="AC7">
+        <v>-0.005594332388172855</v>
+      </c>
+      <c r="AD7">
+        <v>6.32</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>6.32</v>
+      </c>
+      <c r="AG7">
+        <v>0.4800000000000004</v>
+      </c>
+      <c r="AH7">
+        <v>0.05542887212769689</v>
+      </c>
+      <c r="AI7">
+        <v>0.2447714949651433</v>
+      </c>
+      <c r="AJ7">
+        <v>0.004437049362174158</v>
+      </c>
+      <c r="AK7">
+        <v>0.02402402402402404</v>
+      </c>
+      <c r="AL7">
+        <v>0.211</v>
+      </c>
+      <c r="AM7">
+        <v>0.173</v>
+      </c>
+      <c r="AN7">
+        <v>3.113300492610838</v>
+      </c>
+      <c r="AO7">
+        <v>5.781990521327014</v>
+      </c>
+      <c r="AP7">
+        <v>0.2364532019704436</v>
+      </c>
+      <c r="AQ7">
+        <v>7.052023121387283</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Yuanta Financial Holding Co., Ltd. (TWSE:2885)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0291</v>
+      </c>
+      <c r="E8">
+        <v>0.0467</v>
+      </c>
+      <c r="G8">
+        <v>0.0959951292112028</v>
+      </c>
+      <c r="H8">
+        <v>0.0959951292112028</v>
+      </c>
+      <c r="I8">
+        <v>0.1771523925494971</v>
+      </c>
+      <c r="J8">
+        <v>0.1494445789965379</v>
+      </c>
+      <c r="K8">
+        <v>788.8</v>
+      </c>
+      <c r="L8">
+        <v>0.1778739908898209</v>
+      </c>
+      <c r="M8">
+        <v>310.8</v>
+      </c>
+      <c r="N8">
+        <v>0.02718969800888827</v>
+      </c>
+      <c r="O8">
+        <v>0.3940162271805274</v>
+      </c>
+      <c r="P8">
+        <v>310.8</v>
+      </c>
+      <c r="Q8">
+        <v>0.02718969800888827</v>
+      </c>
+      <c r="R8">
+        <v>0.3940162271805274</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>2374.6</v>
+      </c>
+      <c r="V8">
+        <v>0.2077369912866991</v>
+      </c>
+      <c r="W8">
+        <v>0.100861826458328</v>
+      </c>
+      <c r="X8">
+        <v>0.06600750332085681</v>
+      </c>
+      <c r="Y8">
+        <v>0.03485432313747118</v>
+      </c>
+      <c r="Z8">
+        <v>0.2316673719184416</v>
+      </c>
+      <c r="AA8">
+        <v>0.03462143286358586</v>
+      </c>
+      <c r="AB8">
+        <v>0.05182233946319605</v>
+      </c>
+      <c r="AC8">
+        <v>-0.01720090659961018</v>
+      </c>
+      <c r="AD8">
+        <v>15349.5</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>15349.5</v>
+      </c>
+      <c r="AG8">
+        <v>12974.9</v>
+      </c>
+      <c r="AH8">
+        <v>0.5731638555206626</v>
+      </c>
+      <c r="AI8">
+        <v>0.6227002949302025</v>
+      </c>
+      <c r="AJ8">
+        <v>0.5316340035319619</v>
+      </c>
+      <c r="AK8">
+        <v>0.5824792483153987</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>18.47334215910459</v>
+      </c>
+      <c r="AP8">
+        <v>15.61547719340474</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Yulon Finance Corporation (TWSE:9941)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.115</v>
+      </c>
+      <c r="E9">
+        <v>0.217</v>
+      </c>
+      <c r="G9">
+        <v>0.2327920792079208</v>
+      </c>
+      <c r="H9">
+        <v>0.2327920792079208</v>
+      </c>
+      <c r="I9">
+        <v>0.2156831683168317</v>
+      </c>
+      <c r="J9">
+        <v>0.164814496543994</v>
+      </c>
+      <c r="K9">
+        <v>204.5</v>
+      </c>
+      <c r="L9">
+        <v>0.161980198019802</v>
+      </c>
+      <c r="M9">
+        <v>86.7</v>
+      </c>
+      <c r="N9">
+        <v>0.02203135720275455</v>
+      </c>
+      <c r="O9">
+        <v>0.423960880195599</v>
+      </c>
+      <c r="P9">
+        <v>86.7</v>
+      </c>
+      <c r="Q9">
+        <v>0.02203135720275455</v>
+      </c>
+      <c r="R9">
+        <v>0.423960880195599</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>231.7</v>
+      </c>
+      <c r="V9">
+        <v>0.05887734099052169</v>
+      </c>
+      <c r="W9">
+        <v>0.2078885839178611</v>
+      </c>
+      <c r="X9">
+        <v>0.07177084397699379</v>
+      </c>
+      <c r="Y9">
+        <v>0.1361177399408673</v>
+      </c>
+      <c r="Z9">
+        <v>0.1705873609966355</v>
+      </c>
+      <c r="AA9">
+        <v>0.02811527001942905</v>
+      </c>
+      <c r="AB9">
+        <v>0.05180898638330675</v>
+      </c>
+      <c r="AC9">
+        <v>-0.0236937163638777</v>
+      </c>
+      <c r="AD9">
+        <v>7445.8</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>7445.8</v>
+      </c>
+      <c r="AG9">
+        <v>7214.1</v>
+      </c>
+      <c r="AH9">
+        <v>0.654224987039917</v>
+      </c>
+      <c r="AI9">
+        <v>0.8627210159200982</v>
+      </c>
+      <c r="AJ9">
+        <v>0.6470393025633666</v>
+      </c>
+      <c r="AK9">
+        <v>0.8589339080117635</v>
+      </c>
+      <c r="AL9">
+        <v>1.03</v>
+      </c>
+      <c r="AM9">
+        <v>1.03</v>
+      </c>
+      <c r="AN9">
+        <v>25.36035422343324</v>
+      </c>
+      <c r="AO9">
+        <v>264.3689320388349</v>
+      </c>
+      <c r="AP9">
+        <v>24.57118528610354</v>
+      </c>
+      <c r="AQ9">
+        <v>264.3689320388349</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>IBF Financial Holdings Co., Ltd. (TWSE:2889)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.0472</v>
-      </c>
-      <c r="E7">
-        <v>0.0032</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>63.4</v>
-      </c>
-      <c r="L7">
-        <v>0.2912264584290308</v>
-      </c>
-      <c r="M7">
-        <v>61.3</v>
-      </c>
-      <c r="N7">
-        <v>0.04834384858044164</v>
-      </c>
-      <c r="O7">
-        <v>0.9668769716088328</v>
-      </c>
-      <c r="P7">
-        <v>61.3</v>
-      </c>
-      <c r="Q7">
-        <v>0.04834384858044164</v>
-      </c>
-      <c r="R7">
-        <v>0.9668769716088328</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>102.9</v>
-      </c>
-      <c r="V7">
-        <v>0.08115141955835962</v>
-      </c>
-      <c r="W7">
-        <v>0.04586226851851852</v>
-      </c>
-      <c r="X7">
-        <v>0.1139574417415955</v>
-      </c>
-      <c r="Y7">
-        <v>-0.06809517322307702</v>
-      </c>
-      <c r="Z7">
-        <v>0.02045962255426687</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.05215523354458076</v>
-      </c>
-      <c r="AC7">
-        <v>-0.05215523354458076</v>
-      </c>
-      <c r="AD7">
-        <v>9276.299999999999</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>9276.299999999999</v>
-      </c>
-      <c r="AG7">
-        <v>9173.4</v>
-      </c>
-      <c r="AH7">
-        <v>0.8797454548903199</v>
-      </c>
-      <c r="AI7">
-        <v>0.8858277867435709</v>
-      </c>
-      <c r="AJ7">
-        <v>0.8785603463137127</v>
-      </c>
-      <c r="AK7">
-        <v>0.8846947632365705</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
+      <c r="D10">
+        <v>0.0416</v>
+      </c>
+      <c r="E10">
+        <v>-0.0534</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>52.3</v>
+      </c>
+      <c r="L10">
+        <v>0.2522913651712494</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>109.5</v>
+      </c>
+      <c r="V10">
+        <v>0.07613154418410624</v>
+      </c>
+      <c r="W10">
+        <v>0.05081616789739603</v>
+      </c>
+      <c r="X10">
+        <v>0.1149676508627544</v>
+      </c>
+      <c r="Y10">
+        <v>-0.06415148296535839</v>
+      </c>
+      <c r="Z10">
+        <v>0.02032853182498831</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.05177553107626978</v>
+      </c>
+      <c r="AC10">
+        <v>-0.05177553107626978</v>
+      </c>
+      <c r="AD10">
+        <v>8642.200000000001</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>8642.200000000001</v>
+      </c>
+      <c r="AG10">
+        <v>8532.700000000001</v>
+      </c>
+      <c r="AH10">
+        <v>0.8573185853876296</v>
+      </c>
+      <c r="AI10">
+        <v>0.859458599359548</v>
+      </c>
+      <c r="AJ10">
+        <v>0.8557516798716278</v>
+      </c>
+      <c r="AK10">
+        <v>0.8579113001337234</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hotai Finance Co., Ltd. (TWSE:6592)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.191</v>
+      </c>
+      <c r="E11">
+        <v>0.169</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>115.5</v>
+      </c>
+      <c r="L11">
+        <v>0.153938424630148</v>
+      </c>
+      <c r="M11">
+        <v>57.8</v>
+      </c>
+      <c r="N11">
+        <v>0.02075776620578201</v>
+      </c>
+      <c r="O11">
+        <v>0.5004329004329005</v>
+      </c>
+      <c r="P11">
+        <v>57.8</v>
+      </c>
+      <c r="Q11">
+        <v>0.02075776620578201</v>
+      </c>
+      <c r="R11">
+        <v>0.5004329004329005</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>170</v>
+      </c>
+      <c r="V11">
+        <v>0.06105225354641767</v>
+      </c>
+      <c r="W11">
+        <v>0.1308633582596873</v>
+      </c>
+      <c r="X11">
+        <v>0.08154964844247339</v>
+      </c>
+      <c r="Y11">
+        <v>0.04931370981721389</v>
+      </c>
+      <c r="Z11">
+        <v>0.1064089291032605</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.05179510543720496</v>
+      </c>
+      <c r="AC11">
+        <v>-0.05179510543720496</v>
+      </c>
+      <c r="AD11">
+        <v>7863.3</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>7863.3</v>
+      </c>
+      <c r="AG11">
+        <v>7693.3</v>
+      </c>
+      <c r="AH11">
+        <v>0.7384905802137531</v>
+      </c>
+      <c r="AI11">
+        <v>0.8658591642349832</v>
+      </c>
+      <c r="AJ11">
+        <v>0.7342476474068985</v>
+      </c>
+      <c r="AK11">
+        <v>0.8633002300398361</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>-0.79</v>
+      </c>
+      <c r="AQ11">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chailease Holding Company Limited (TWSE:5871)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.09539999999999998</v>
+      </c>
+      <c r="E12">
+        <v>0.15</v>
+      </c>
+      <c r="F12">
+        <v>0.149</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>790.1</v>
+      </c>
+      <c r="L12">
+        <v>0.4015960150452373</v>
+      </c>
+      <c r="M12">
+        <v>314.847</v>
+      </c>
+      <c r="N12">
+        <v>0.03095627636249225</v>
+      </c>
+      <c r="O12">
+        <v>0.3984900645487913</v>
+      </c>
+      <c r="P12">
+        <v>314.847</v>
+      </c>
+      <c r="Q12">
+        <v>0.03095627636249225</v>
+      </c>
+      <c r="R12">
+        <v>0.3984900645487913</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>994.6</v>
+      </c>
+      <c r="V12">
+        <v>0.09779071253699352</v>
+      </c>
+      <c r="W12">
+        <v>0.1862213632506835</v>
+      </c>
+      <c r="X12">
+        <v>0.07352157091269197</v>
+      </c>
+      <c r="Y12">
+        <v>0.1126997923379915</v>
+      </c>
+      <c r="Z12">
+        <v>0.09201928878453529</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.05180587967942727</v>
+      </c>
+      <c r="AC12">
+        <v>-0.05180587967942727</v>
+      </c>
+      <c r="AD12">
+        <v>20940.4</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>20940.4</v>
+      </c>
+      <c r="AG12">
+        <v>19945.8</v>
+      </c>
+      <c r="AH12">
+        <v>0.6730845261016165</v>
+      </c>
+      <c r="AI12">
+        <v>0.8083161559781057</v>
+      </c>
+      <c r="AJ12">
+        <v>0.6622881144887355</v>
+      </c>
+      <c r="AK12">
+        <v>0.8006631448802968</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-17.7</v>
+      </c>
+      <c r="AQ12">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Forward Graphic Enterprise Co., Ltd. (TPEX:8906)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.028</v>
+      </c>
+      <c r="G13">
+        <v>-0.02923976608187135</v>
+      </c>
+      <c r="H13">
+        <v>-0.02923976608187135</v>
+      </c>
+      <c r="I13">
+        <v>-0.1242690058479532</v>
+      </c>
+      <c r="J13">
+        <v>-0.1242690058479532</v>
+      </c>
+      <c r="K13">
+        <v>-1.03</v>
+      </c>
+      <c r="L13">
+        <v>-0.1505847953216374</v>
+      </c>
+      <c r="M13">
+        <v>0.1</v>
+      </c>
+      <c r="N13">
+        <v>0.00574712643678161</v>
+      </c>
+      <c r="O13">
+        <v>-0.0970873786407767</v>
+      </c>
+      <c r="P13">
+        <v>0.1</v>
+      </c>
+      <c r="Q13">
+        <v>0.00574712643678161</v>
+      </c>
+      <c r="R13">
+        <v>-0.0970873786407767</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>1.05</v>
+      </c>
+      <c r="V13">
+        <v>0.06034482758620691</v>
+      </c>
+      <c r="W13">
+        <v>-0.08879310344827587</v>
+      </c>
+      <c r="X13">
+        <v>0.06832023912799592</v>
+      </c>
+      <c r="Y13">
+        <v>-0.1571133425762718</v>
+      </c>
+      <c r="Z13">
+        <v>0.1932367149758454</v>
+      </c>
+      <c r="AA13">
+        <v>-0.0240133344633726</v>
+      </c>
+      <c r="AB13">
+        <v>0.05181629366057276</v>
+      </c>
+      <c r="AC13">
+        <v>-0.07582962812394536</v>
+      </c>
+      <c r="AD13">
+        <v>27.2</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>27.2</v>
+      </c>
+      <c r="AG13">
+        <v>26.15</v>
+      </c>
+      <c r="AH13">
+        <v>0.609865470852018</v>
+      </c>
+      <c r="AI13">
+        <v>0.7214854111405835</v>
+      </c>
+      <c r="AJ13">
+        <v>0.600459242250287</v>
+      </c>
+      <c r="AK13">
+        <v>0.7135061391541609</v>
+      </c>
+      <c r="AL13">
+        <v>0.397</v>
+      </c>
+      <c r="AM13">
+        <v>0.28</v>
+      </c>
+      <c r="AN13">
+        <v>-57.38396624472574</v>
+      </c>
+      <c r="AO13">
+        <v>-2.141057934508816</v>
+      </c>
+      <c r="AP13">
+        <v>-55.16877637130801</v>
+      </c>
+      <c r="AQ13">
+        <v>-3.035714285714285</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Shen's Art Printing Co., Ltd. (TPEX:8921)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.0528</v>
+      </c>
+      <c r="G14">
+        <v>0.02663507109004739</v>
+      </c>
+      <c r="H14">
+        <v>0.02398104265402843</v>
+      </c>
+      <c r="I14">
+        <v>-0.03838862559241706</v>
+      </c>
+      <c r="J14">
+        <v>-0.03838862559241706</v>
+      </c>
+      <c r="K14">
+        <v>-0.272</v>
+      </c>
+      <c r="L14">
+        <v>-0.01289099526066351</v>
+      </c>
+      <c r="M14">
+        <v>0.73</v>
+      </c>
+      <c r="N14">
+        <v>0.0336405529953917</v>
+      </c>
+      <c r="O14">
+        <v>-2.683823529411764</v>
+      </c>
+      <c r="P14">
+        <v>0.73</v>
+      </c>
+      <c r="Q14">
+        <v>0.0336405529953917</v>
+      </c>
+      <c r="R14">
+        <v>-2.683823529411764</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>4.83</v>
+      </c>
+      <c r="V14">
+        <v>0.2225806451612903</v>
+      </c>
+      <c r="W14">
+        <v>-0.009283276450511945</v>
+      </c>
+      <c r="X14">
+        <v>0.05324172957744167</v>
+      </c>
+      <c r="Y14">
+        <v>-0.06252500602795362</v>
+      </c>
+      <c r="Z14">
+        <v>0.7935314027830012</v>
+      </c>
+      <c r="AA14">
+        <v>-0.03046257991726213</v>
+      </c>
+      <c r="AB14">
+        <v>0.05189828796756082</v>
+      </c>
+      <c r="AC14">
+        <v>-0.08236086788482296</v>
+      </c>
+      <c r="AD14">
+        <v>2.74</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>2.74</v>
+      </c>
+      <c r="AG14">
+        <v>-2.09</v>
+      </c>
+      <c r="AH14">
+        <v>0.1121112929623568</v>
+      </c>
+      <c r="AI14">
+        <v>0.08578584846587353</v>
+      </c>
+      <c r="AJ14">
+        <v>-0.1065782763895971</v>
+      </c>
+      <c r="AK14">
+        <v>-0.07709332349686462</v>
+      </c>
+      <c r="AL14">
+        <v>0.077</v>
+      </c>
+      <c r="AM14">
+        <v>-0.298</v>
+      </c>
+      <c r="AN14">
+        <v>9.256756756756758</v>
+      </c>
+      <c r="AO14">
+        <v>-10.51948051948052</v>
+      </c>
+      <c r="AP14">
+        <v>-7.060810810810811</v>
+      </c>
+      <c r="AQ14">
+        <v>2.718120805369128</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Choice Development, Inc. (TWSE:9929)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>-0.0118</v>
+      </c>
+      <c r="E15">
+        <v>0.129</v>
+      </c>
+      <c r="G15">
+        <v>-0.1690140845070423</v>
+      </c>
+      <c r="H15">
+        <v>-0.1690140845070423</v>
+      </c>
+      <c r="I15">
+        <v>-0.09812206572769952</v>
+      </c>
+      <c r="J15">
+        <v>-0.09601515020593911</v>
+      </c>
+      <c r="K15">
+        <v>0.98</v>
+      </c>
+      <c r="L15">
+        <v>0.0460093896713615</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>12.5</v>
+      </c>
+      <c r="V15">
+        <v>0.2212389380530974</v>
+      </c>
+      <c r="W15">
+        <v>0.03576642335766424</v>
+      </c>
+      <c r="X15">
+        <v>0.05828708831471033</v>
+      </c>
+      <c r="Y15">
+        <v>-0.0225206649570461</v>
+      </c>
+      <c r="Z15">
+        <v>0.7395833333333335</v>
+      </c>
+      <c r="AA15">
+        <v>-0.07101120483980915</v>
+      </c>
+      <c r="AB15">
+        <v>0.0518545291533377</v>
+      </c>
+      <c r="AC15">
+        <v>-0.1228657339931468</v>
+      </c>
+      <c r="AD15">
+        <v>34.3</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>34.3</v>
+      </c>
+      <c r="AG15">
+        <v>21.8</v>
+      </c>
+      <c r="AH15">
+        <v>0.3777533039647577</v>
+      </c>
+      <c r="AI15">
+        <v>0.518910741301059</v>
+      </c>
+      <c r="AJ15">
+        <v>0.2784163473818646</v>
+      </c>
+      <c r="AK15">
+        <v>0.4067164179104478</v>
+      </c>
+      <c r="AL15">
+        <v>0.451</v>
+      </c>
+      <c r="AM15">
+        <v>0.172</v>
+      </c>
+      <c r="AN15">
+        <v>-20.41666666666666</v>
+      </c>
+      <c r="AO15">
+        <v>-4.634146341463414</v>
+      </c>
+      <c r="AP15">
+        <v>-12.97619047619047</v>
+      </c>
+      <c r="AQ15">
+        <v>-12.15116279069767</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O'Pay Electronic Payment Co., Ltd. (TPEX:6878)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>-1.36039886039886</v>
+      </c>
+      <c r="H16">
+        <v>-1.98005698005698</v>
+      </c>
+      <c r="I16">
+        <v>-2.934472934472935</v>
+      </c>
+      <c r="J16">
+        <v>-2.934472934472935</v>
+      </c>
+      <c r="K16">
+        <v>-1.65</v>
+      </c>
+      <c r="L16">
+        <v>-2.350427350427351</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>2.97</v>
+      </c>
+      <c r="V16">
+        <v>0.05201401050788091</v>
+      </c>
+      <c r="W16">
+        <v>-0.06790123456790123</v>
+      </c>
+      <c r="X16">
+        <v>0.05191675589446192</v>
+      </c>
+      <c r="Y16">
+        <v>-0.1198179904623632</v>
+      </c>
+      <c r="Z16">
+        <v>0.03421052631578947</v>
+      </c>
+      <c r="AA16">
+        <v>-0.1003898635477583</v>
+      </c>
+      <c r="AB16">
+        <v>0.05191675589446192</v>
+      </c>
+      <c r="AC16">
+        <v>-0.1523066194422202</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>-2.97</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.05486791058562719</v>
+      </c>
+      <c r="AK16">
+        <v>-0.1594202898550725</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-0.295</v>
+      </c>
+      <c r="AN16">
+        <v>-0</v>
+      </c>
+      <c r="AP16">
+        <v>1.477611940298508</v>
+      </c>
+      <c r="AQ16">
+        <v>6.983050847457628</v>
       </c>
     </row>
   </sheetData>
